--- a/PFP-C/Input data and Generated Schedule/180.xlsx
+++ b/PFP-C/Input data and Generated Schedule/180.xlsx
@@ -48203,7 +48203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48228,7 +48228,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>objective all vehicle travel individually</t>
+          <t>objective_all_vehicle_travel_individually</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -48238,7 +48238,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>objective LLA</t>
+          <t>objective_LLA</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -48248,11 +48248,131 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>objective lb</t>
+          <t>objective_lb</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>84.09100000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_5</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_5</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_10</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_10</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_15</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_15</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_20</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_20</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_25</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_25</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_30</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_30</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -69147,7 +69267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69183,25 +69303,20 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>before_due_time_(minute)</t>
+          <t>duration_trip_alone_(minute)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>duration_trip_alone_(minute)</t>
+          <t>Saving_time_(minute)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Saving_time_(minute)</t>
+          <t>Saving_time(%)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Saving_time(%)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Exit</t>
         </is>
@@ -69234,18 +69349,15 @@
         <v>1.138461538461536</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>282.0382882882882</v>
       </c>
       <c r="I2" t="n">
-        <v>282.0382882882882</v>
+        <v>0.5555555555555544</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5555555555555544</v>
-      </c>
-      <c r="K2" t="n">
         <v>0.1969787715445528</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -69278,18 +69390,15 @@
         <v>8.184615384615372</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>281.4376876876876</v>
       </c>
       <c r="I3" t="n">
-        <v>281.4376876876876</v>
+        <v>3.993993993993987</v>
       </c>
       <c r="J3" t="n">
-        <v>3.993993993993987</v>
-      </c>
-      <c r="K3" t="n">
         <v>1.419139713237744</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -69322,18 +69431,15 @@
         <v>8.908554572271374</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>305.4512012012012</v>
       </c>
       <c r="I4" t="n">
-        <v>305.4512012012012</v>
+        <v>4.534534534534528</v>
       </c>
       <c r="J4" t="n">
-        <v>4.534534534534528</v>
-      </c>
-      <c r="K4" t="n">
         <v>1.48453648789144</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -69366,18 +69472,15 @@
         <v>9.999999999999988</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>244.8460960960962</v>
       </c>
       <c r="I5" t="n">
-        <v>244.8460960960962</v>
+        <v>3.978978978978974</v>
       </c>
       <c r="J5" t="n">
-        <v>3.978978978978974</v>
-      </c>
-      <c r="K5" t="n">
         <v>1.625093902831647</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -69410,18 +69513,15 @@
         <v>8.184615384615372</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>273.9301801801802</v>
       </c>
       <c r="I6" t="n">
-        <v>273.9301801801802</v>
+        <v>3.993993993993987</v>
       </c>
       <c r="J6" t="n">
-        <v>3.993993993993987</v>
-      </c>
-      <c r="K6" t="n">
         <v>1.458033573141484</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -69454,18 +69554,15 @@
         <v>1.396226415094337</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>213.3145645645645</v>
       </c>
       <c r="I7" t="n">
-        <v>213.3145645645645</v>
+        <v>0.5555555555555544</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5555555555555544</v>
-      </c>
-      <c r="K7" t="n">
         <v>0.260439579777218</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -69498,18 +69595,15 @@
         <v>6.155507559395232</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>397.25</v>
       </c>
       <c r="I8" t="n">
-        <v>397.25</v>
+        <v>4.279279279279268</v>
       </c>
       <c r="J8" t="n">
-        <v>4.279279279279268</v>
-      </c>
-      <c r="K8" t="n">
         <v>1.077225746829268</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -69542,18 +69636,15 @@
         <v>8.228228228228202</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>288.3385885885886</v>
       </c>
       <c r="I9" t="n">
-        <v>288.3385885885886</v>
+        <v>4.114114114114101</v>
       </c>
       <c r="J9" t="n">
-        <v>4.114114114114101</v>
-      </c>
-      <c r="K9" t="n">
         <v>1.426834380459655</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -69586,18 +69677,15 @@
         <v>9.999999999999986</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>310.256006006006</v>
       </c>
       <c r="I10" t="n">
-        <v>310.256006006006</v>
+        <v>5.090090090090082</v>
       </c>
       <c r="J10" t="n">
-        <v>5.090090090090082</v>
-      </c>
-      <c r="K10" t="n">
         <v>1.640609687340443</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -69630,18 +69718,15 @@
         <v>7.951388888888877</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>263.7477477477477</v>
       </c>
       <c r="I11" t="n">
-        <v>263.7477477477477</v>
+        <v>3.438438438438433</v>
       </c>
       <c r="J11" t="n">
-        <v>3.438438438438433</v>
-      </c>
-      <c r="K11" t="n">
         <v>1.30368447419957</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -69674,18 +69759,15 @@
         <v>1.225165562913905</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>253.527027027027</v>
       </c>
       <c r="I12" t="n">
-        <v>253.527027027027</v>
+        <v>0.5555555555555544</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5555555555555544</v>
-      </c>
-      <c r="K12" t="n">
         <v>0.2191307025804117</v>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -69718,18 +69800,15 @@
         <v>8.519999999999985</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>424.5495495495495</v>
       </c>
       <c r="I13" t="n">
-        <v>424.5495495495495</v>
+        <v>6.396396396396384</v>
       </c>
       <c r="J13" t="n">
-        <v>6.396396396396384</v>
-      </c>
-      <c r="K13" t="n">
         <v>1.506631299734745</v>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -69762,18 +69841,15 @@
         <v>3.543543543543527</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>277.828078078078</v>
       </c>
       <c r="I14" t="n">
-        <v>277.828078078078</v>
+        <v>1.771771771771763</v>
       </c>
       <c r="J14" t="n">
-        <v>1.771771771771763</v>
-      </c>
-      <c r="K14" t="n">
         <v>0.6377223583837491</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -69806,18 +69882,15 @@
         <v>9.259999999999984</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>447.072072072072</v>
       </c>
       <c r="I15" t="n">
-        <v>447.072072072072</v>
+        <v>6.951951951951939</v>
       </c>
       <c r="J15" t="n">
-        <v>6.951951951951939</v>
-      </c>
-      <c r="K15" t="n">
         <v>1.554995801847185</v>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -69850,18 +69923,15 @@
         <v>8.184615384615372</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>282.3385885885886</v>
       </c>
       <c r="I16" t="n">
-        <v>282.3385885885886</v>
+        <v>3.993993993993987</v>
       </c>
       <c r="J16" t="n">
-        <v>3.993993993993987</v>
-      </c>
-      <c r="K16" t="n">
         <v>1.414611447184735</v>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -69894,18 +69964,15 @@
         <v>8.977900552486167</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>322.2507507507507</v>
       </c>
       <c r="I17" t="n">
-        <v>322.2507507507507</v>
+        <v>4.879879879879868</v>
       </c>
       <c r="J17" t="n">
-        <v>4.879879879879868</v>
-      </c>
-      <c r="K17" t="n">
         <v>1.514311407657287</v>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -69938,18 +70005,15 @@
         <v>9.999999999999984</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>344.753003003003</v>
       </c>
       <c r="I18" t="n">
-        <v>344.753003003003</v>
+        <v>5.840840840840831</v>
       </c>
       <c r="J18" t="n">
-        <v>5.840840840840831</v>
-      </c>
-      <c r="K18" t="n">
         <v>1.694210286774487</v>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -69982,18 +70046,15 @@
         <v>9.999999999999984</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>337.2454954954955</v>
       </c>
       <c r="I19" t="n">
-        <v>337.2454954954955</v>
+        <v>5.840840840840831</v>
       </c>
       <c r="J19" t="n">
-        <v>5.840840840840831</v>
-      </c>
-      <c r="K19" t="n">
         <v>1.731925531654387</v>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -70026,18 +70087,15 @@
         <v>9.99999999999998</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>300.9512012012012</v>
       </c>
       <c r="I20" t="n">
-        <v>300.9512012012012</v>
+        <v>4.999999999999989</v>
       </c>
       <c r="J20" t="n">
-        <v>4.999999999999989</v>
-      </c>
-      <c r="K20" t="n">
         <v>1.661398917845566</v>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -70070,18 +70128,15 @@
         <v>8.908554572271374</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>308.1539039039039</v>
       </c>
       <c r="I21" t="n">
-        <v>308.1539039039039</v>
+        <v>4.534534534534528</v>
       </c>
       <c r="J21" t="n">
-        <v>4.534534534534528</v>
-      </c>
-      <c r="K21" t="n">
         <v>1.471516173278336</v>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -70114,18 +70169,15 @@
         <v>2.587719298245602</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>184.8138138138138</v>
       </c>
       <c r="I22" t="n">
-        <v>184.8138138138138</v>
+        <v>0.8858858858858816</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8858858858858816</v>
-      </c>
-      <c r="K22" t="n">
         <v>0.479339648700906</v>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -70158,18 +70210,15 @@
         <v>9.259999999999984</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>427.8528528528528</v>
       </c>
       <c r="I23" t="n">
-        <v>427.8528528528528</v>
+        <v>6.951951951951939</v>
       </c>
       <c r="J23" t="n">
-        <v>6.951951951951939</v>
-      </c>
-      <c r="K23" t="n">
         <v>1.624846464291978</v>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -70202,18 +70251,15 @@
         <v>2.182890855457222</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>302.1478978978978</v>
       </c>
       <c r="I24" t="n">
-        <v>302.1478978978978</v>
+        <v>1.111111111111109</v>
       </c>
       <c r="J24" t="n">
-        <v>1.111111111111109</v>
-      </c>
-      <c r="K24" t="n">
         <v>0.3677374950616326</v>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -70246,18 +70292,15 @@
         <v>9.999999999999982</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>438.9639639639639</v>
       </c>
       <c r="I25" t="n">
-        <v>438.9639639639639</v>
+        <v>7.507507507507493</v>
       </c>
       <c r="J25" t="n">
-        <v>7.507507507507493</v>
-      </c>
-      <c r="K25" t="n">
         <v>1.710278775440394</v>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -70290,18 +70333,15 @@
         <v>9.999999999999979</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>294.0503003003003</v>
       </c>
       <c r="I26" t="n">
-        <v>294.0503003003003</v>
+        <v>4.879879879879868</v>
       </c>
       <c r="J26" t="n">
-        <v>4.879879879879868</v>
-      </c>
-      <c r="K26" t="n">
         <v>1.659539158741299</v>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -70334,18 +70374,15 @@
         <v>8.615023474178393</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>362.1426426426427</v>
       </c>
       <c r="I27" t="n">
-        <v>362.1426426426427</v>
+        <v>5.510510510510503</v>
       </c>
       <c r="J27" t="n">
-        <v>5.510510510510503</v>
-      </c>
-      <c r="K27" t="n">
         <v>1.521640884458945</v>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -70378,18 +70415,15 @@
         <v>7.926565874730021</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>402.3551051051051</v>
       </c>
       <c r="I28" t="n">
-        <v>402.3551051051051</v>
+        <v>5.510510510510509</v>
       </c>
       <c r="J28" t="n">
-        <v>5.510510510510509</v>
-      </c>
-      <c r="K28" t="n">
         <v>1.369563959943053</v>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -70422,18 +70456,15 @@
         <v>8.908554572271374</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>307.253003003003</v>
       </c>
       <c r="I29" t="n">
-        <v>307.253003003003</v>
+        <v>4.534534534534528</v>
       </c>
       <c r="J29" t="n">
-        <v>4.534534534534528</v>
-      </c>
-      <c r="K29" t="n">
         <v>1.475830826782907</v>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -70466,18 +70497,15 @@
         <v>3.033419023136232</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>323.1313813813813</v>
       </c>
       <c r="I30" t="n">
-        <v>323.1313813813813</v>
+        <v>1.771771771771763</v>
       </c>
       <c r="J30" t="n">
-        <v>1.771771771771763</v>
-      </c>
-      <c r="K30" t="n">
         <v>0.5483131239675539</v>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -70510,18 +70538,15 @@
         <v>8.725701943844491</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>387.3400900900901</v>
       </c>
       <c r="I31" t="n">
-        <v>387.3400900900901</v>
+        <v>6.066066066066064</v>
       </c>
       <c r="J31" t="n">
-        <v>6.066066066066064</v>
-      </c>
-      <c r="K31" t="n">
         <v>1.566082680637364</v>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -70554,18 +70579,15 @@
         <v>8.908554572271374</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>303.349099099099</v>
       </c>
       <c r="I32" t="n">
-        <v>303.349099099099</v>
+        <v>4.534534534534528</v>
       </c>
       <c r="J32" t="n">
-        <v>4.534534534534528</v>
-      </c>
-      <c r="K32" t="n">
         <v>1.494823801356724</v>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -70598,18 +70620,15 @@
         <v>8.908554572271374</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>323.7695195195194</v>
       </c>
       <c r="I33" t="n">
-        <v>323.7695195195194</v>
+        <v>4.534534534534528</v>
       </c>
       <c r="J33" t="n">
-        <v>4.534534534534528</v>
-      </c>
-      <c r="K33" t="n">
         <v>1.40054398612441</v>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -70642,18 +70661,15 @@
         <v>8.228228228228202</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>291.0412912912913</v>
       </c>
       <c r="I34" t="n">
-        <v>291.0412912912913</v>
+        <v>4.114114114114101</v>
       </c>
       <c r="J34" t="n">
-        <v>4.114114114114101</v>
-      </c>
-      <c r="K34" t="n">
         <v>1.413584339136419</v>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -70686,18 +70702,15 @@
         <v>8.908554572271374</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>306.0518018018018</v>
       </c>
       <c r="I35" t="n">
-        <v>306.0518018018018</v>
+        <v>4.534534534534528</v>
       </c>
       <c r="J35" t="n">
-        <v>4.534534534534528</v>
-      </c>
-      <c r="K35" t="n">
         <v>1.481623211442839</v>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -70730,18 +70743,15 @@
         <v>7.951388888888877</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>266.4504504504504</v>
       </c>
       <c r="I36" t="n">
-        <v>266.4504504504504</v>
+        <v>3.438438438438433</v>
       </c>
       <c r="J36" t="n">
-        <v>3.438438438438433</v>
-      </c>
-      <c r="K36" t="n">
         <v>1.290460733928408</v>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -70774,18 +70784,15 @@
         <v>9.999999999999979</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>291.0472972972973</v>
       </c>
       <c r="I37" t="n">
-        <v>291.0472972972973</v>
+        <v>4.879879879879868</v>
       </c>
       <c r="J37" t="n">
-        <v>4.879879879879868</v>
-      </c>
-      <c r="K37" t="n">
         <v>1.676662152576252</v>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -70818,18 +70825,15 @@
         <v>7.926565874730021</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>415.268018018018</v>
       </c>
       <c r="I38" t="n">
-        <v>415.268018018018</v>
+        <v>5.510510510510509</v>
       </c>
       <c r="J38" t="n">
-        <v>5.510510510510509</v>
-      </c>
-      <c r="K38" t="n">
         <v>1.326976861066969</v>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -70862,18 +70866,15 @@
         <v>9.999999999999986</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>303.6493993993994</v>
       </c>
       <c r="I39" t="n">
-        <v>303.6493993993994</v>
+        <v>5.090090090090082</v>
       </c>
       <c r="J39" t="n">
-        <v>5.090090090090082</v>
-      </c>
-      <c r="K39" t="n">
         <v>1.676305008393885</v>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -70906,18 +70907,15 @@
         <v>2.953846153846142</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>284.4406906906908</v>
       </c>
       <c r="I40" t="n">
-        <v>284.4406906906908</v>
+        <v>1.441441441441436</v>
       </c>
       <c r="J40" t="n">
-        <v>1.441441441441436</v>
-      </c>
-      <c r="K40" t="n">
         <v>0.506763444407784</v>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -70950,18 +70948,15 @@
         <v>9.999999999999986</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>320.1659159159159</v>
       </c>
       <c r="I41" t="n">
-        <v>320.1659159159159</v>
+        <v>5.090090090090082</v>
       </c>
       <c r="J41" t="n">
-        <v>5.090090090090082</v>
-      </c>
-      <c r="K41" t="n">
         <v>1.589828847186493</v>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -70994,18 +70989,15 @@
         <v>6.821192052980117</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>273.6471471471472</v>
       </c>
       <c r="I42" t="n">
-        <v>273.6471471471472</v>
+        <v>3.093093093093085</v>
       </c>
       <c r="J42" t="n">
-        <v>3.093093093093085</v>
-      </c>
-      <c r="K42" t="n">
         <v>1.130321702725389</v>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -71038,18 +71030,15 @@
         <v>6.810810810810794</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>331.5540540540541</v>
       </c>
       <c r="I43" t="n">
-        <v>331.5540540540541</v>
+        <v>3.783783783783774</v>
       </c>
       <c r="J43" t="n">
-        <v>3.783783783783774</v>
-      </c>
-      <c r="K43" t="n">
         <v>1.141226818830239</v>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -71082,18 +71071,15 @@
         <v>2.594594594594585</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>321.3438438438438</v>
       </c>
       <c r="I44" t="n">
-        <v>321.3438438438438</v>
+        <v>1.441441441441436</v>
       </c>
       <c r="J44" t="n">
-        <v>1.441441441441436</v>
-      </c>
-      <c r="K44" t="n">
         <v>0.4485666892507517</v>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -71126,18 +71112,15 @@
         <v>4.267352185089972</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>342.0503003003003</v>
       </c>
       <c r="I45" t="n">
-        <v>342.0503003003003</v>
+        <v>2.492492492492491</v>
       </c>
       <c r="J45" t="n">
-        <v>2.492492492492491</v>
-      </c>
-      <c r="K45" t="n">
         <v>0.7286918006808436</v>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -71170,18 +71153,15 @@
         <v>7.249357326478127</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>343.5518018018018</v>
       </c>
       <c r="I46" t="n">
-        <v>343.5518018018018</v>
+        <v>4.234234234234221</v>
       </c>
       <c r="J46" t="n">
-        <v>4.234234234234221</v>
-      </c>
-      <c r="K46" t="n">
         <v>1.23248785540557</v>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -71214,18 +71194,15 @@
         <v>1.516709511568116</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>329.4376876876877</v>
       </c>
       <c r="I47" t="n">
-        <v>329.4376876876877</v>
+        <v>0.8858858858858816</v>
       </c>
       <c r="J47" t="n">
-        <v>0.8858858858858816</v>
-      </c>
-      <c r="K47" t="n">
         <v>0.268908482239505</v>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -71258,18 +71235,15 @@
         <v>9.090909090909062</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>351.3460960960961</v>
       </c>
       <c r="I48" t="n">
-        <v>351.3460960960961</v>
+        <v>5.555555555555537</v>
       </c>
       <c r="J48" t="n">
-        <v>5.555555555555537</v>
-      </c>
-      <c r="K48" t="n">
         <v>1.581220231926541</v>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -71302,18 +71276,15 @@
         <v>9.072681704260631</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>352.253003003003</v>
       </c>
       <c r="I49" t="n">
-        <v>352.253003003003</v>
+        <v>5.435435435435423</v>
       </c>
       <c r="J49" t="n">
-        <v>5.435435435435423</v>
-      </c>
-      <c r="K49" t="n">
         <v>1.543048714729931</v>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -71346,18 +71317,15 @@
         <v>6.092544987146521</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>342.9512012012012</v>
       </c>
       <c r="I50" t="n">
-        <v>342.9512012012012</v>
+        <v>3.558558558558553</v>
       </c>
       <c r="J50" t="n">
-        <v>3.558558558558553</v>
-      </c>
-      <c r="K50" t="n">
         <v>1.0376282532601</v>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -71390,18 +71358,15 @@
         <v>2.048611111111101</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>247.8318318318317</v>
       </c>
       <c r="I51" t="n">
-        <v>247.8318318318317</v>
+        <v>0.8858858858858816</v>
       </c>
       <c r="J51" t="n">
-        <v>0.8858858858858816</v>
-      </c>
-      <c r="K51" t="n">
         <v>0.3574544397053105</v>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -71418,7 +71383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71444,20 +71409,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>before_due_time_(minute)</t>
+          <t>duration_trip_alone_(minute)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>duration_trip_alone_(minute)</t>
+          <t>Saving_time_(minute)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Saving_time_(minute)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Saving_time(%)</t>
         </is>
@@ -71490,9 +71450,6 @@
       <c r="H2" t="n">
         <v>50</v>
       </c>
-      <c r="I2" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -71513,15 +71470,12 @@
         <v>7.187154177334403</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>318.6106306306307</v>
       </c>
       <c r="G3" t="n">
-        <v>318.6106306306307</v>
+        <v>3.991291291291284</v>
       </c>
       <c r="H3" t="n">
-        <v>3.991291291291284</v>
-      </c>
-      <c r="I3" t="n">
         <v>1.218986612731886</v>
       </c>
     </row>
@@ -71544,15 +71498,12 @@
         <v>2.929471409385037</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>56.00000736489139</v>
       </c>
       <c r="G4" t="n">
-        <v>56.00000736489139</v>
+        <v>1.844037497723318</v>
       </c>
       <c r="H4" t="n">
-        <v>1.844037497723318</v>
-      </c>
-      <c r="I4" t="n">
         <v>0.4872211137229981</v>
       </c>
     </row>
@@ -71575,15 +71526,12 @@
         <v>1.138461538461536</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>184.8138138138138</v>
       </c>
       <c r="G5" t="n">
-        <v>184.8138138138138</v>
+        <v>0.5555555555555544</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5555555555555544</v>
-      </c>
-      <c r="I5" t="n">
         <v>0.1969787715445528</v>
       </c>
     </row>
@@ -71606,15 +71554,12 @@
         <v>6.108285630208699</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>282.8641141141142</v>
       </c>
       <c r="G6" t="n">
-        <v>282.8641141141142</v>
+        <v>3.179429429429422</v>
       </c>
       <c r="H6" t="n">
-        <v>3.179429429429422</v>
-      </c>
-      <c r="I6" t="n">
         <v>1.047527626652392</v>
       </c>
     </row>
@@ -71637,15 +71582,12 @@
         <v>8.228228228228202</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>307.7034534534534</v>
       </c>
       <c r="G7" t="n">
-        <v>307.7034534534534</v>
+        <v>4.406906906906898</v>
       </c>
       <c r="H7" t="n">
-        <v>4.406906906906898</v>
-      </c>
-      <c r="I7" t="n">
         <v>1.4229870468487</v>
       </c>
     </row>
@@ -71668,15 +71610,12 @@
         <v>9.086352244246953</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>343.4016516516517</v>
       </c>
       <c r="G8" t="n">
-        <v>343.4016516516517</v>
+        <v>5.090090090090082</v>
       </c>
       <c r="H8" t="n">
-        <v>5.090090090090082</v>
-      </c>
-      <c r="I8" t="n">
         <v>1.563310960939819</v>
       </c>
     </row>
@@ -71699,15 +71638,12 @@
         <v>9.999999999999988</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>447.072072072072</v>
       </c>
       <c r="G9" t="n">
-        <v>447.072072072072</v>
+        <v>7.507507507507493</v>
       </c>
       <c r="H9" t="n">
-        <v>7.507507507507493</v>
-      </c>
-      <c r="I9" t="n">
         <v>1.731925531654387</v>
       </c>
     </row>
